--- a/Data/Form_Export_WH.xlsx
+++ b/Data/Form_Export_WH.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tuyenmt\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tuyenmt\Downloads\prj_warehouse_bivn-soft\prj_warehouse_bivn-soft\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{721E264E-DDEC-4E4F-9D3E-D70AF4868348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C016B230-AD3B-4890-A1A3-114F31D52010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2930" yWindow="3350" windowWidth="21600" windowHeight="12670" xr2:uid="{B8127969-015C-44AE-9BA8-F08643412F19}"/>
+    <workbookView xWindow="1100" yWindow="1100" windowWidth="21600" windowHeight="12670" xr2:uid="{B8127969-015C-44AE-9BA8-F08643412F19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>STT</t>
   </si>
@@ -50,13 +50,16 @@
     <t>Số lượng</t>
   </si>
   <si>
-    <t>Nhóm</t>
-  </si>
-  <si>
-    <t>Kho</t>
-  </si>
-  <si>
-    <t>Thời gian hàng về</t>
+    <t xml:space="preserve">Đơn vị </t>
+  </si>
+  <si>
+    <t>Khối</t>
+  </si>
+  <si>
+    <t>Vị trí kho</t>
+  </si>
+  <si>
+    <t>Thời gian</t>
   </si>
 </sst>
 </file>
@@ -447,20 +450,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B60DA8E-9E81-4D25-9DE0-663EE4886162}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.08984375" style="2" customWidth="1"/>
     <col min="2" max="2" width="22.6328125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="43.54296875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="39.81640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="13.1796875" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.54296875" style="2" customWidth="1"/>
     <col min="6" max="6" width="8.90625" style="2" customWidth="1"/>
     <col min="7" max="7" width="22.453125" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.7265625" style="2"/>
+    <col min="8" max="8" width="25.54296875" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -471,16 +475,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
